--- a/Semestre 2/Bureautique/Base attestation.xlsx
+++ b/Semestre 2/Bureautique/Base attestation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ousseynou Sarr\Desktop\Dossier ISI-KMS\Licence 1\Semestre 2\Semestre 2\Bureautique\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAD8E724-5EE7-4BD4-AB03-F8D2E464F19C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7D8F0B-0259-43E1-8BEA-FAE8455F5858}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{F0E1F4C2-8902-49B8-9403-C83380BB1D21}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
   <si>
     <t>Civilité</t>
   </si>
@@ -81,9 +81,6 @@
     <t>BA</t>
   </si>
   <si>
-    <t>Aliou</t>
-  </si>
-  <si>
     <t>Khadi</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Rufisque</t>
   </si>
   <si>
-    <t>Kaolak</t>
-  </si>
-  <si>
     <t>Ziguinchor</t>
   </si>
   <si>
@@ -163,6 +157,18 @@
   </si>
   <si>
     <t>Keur massar</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Saliou</t>
+  </si>
+  <si>
+    <t>Sarr</t>
+  </si>
+  <si>
+    <t>Mbalcam</t>
   </si>
 </sst>
 </file>
@@ -552,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B040E4-95FB-40E5-97F6-7A353DC94BB8}">
-  <dimension ref="A2:H12"/>
+  <dimension ref="A2:I12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
@@ -563,9 +569,10 @@
     <col min="6" max="6" width="26.54296875" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="25.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" s="4" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="4" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -590,8 +597,11 @@
       <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -608,16 +618,19 @@
         <v>44328</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -628,22 +641,25 @@
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2">
         <v>37502</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="I4" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -660,16 +676,19 @@
         <v>36547</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -680,82 +699,91 @@
         <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2">
         <v>37820</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="I6" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2">
-        <v>37204</v>
+        <v>37231</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2">
         <v>37301</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I8" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
@@ -764,47 +792,53 @@
         <v>36765</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2">
         <v>37777</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
@@ -816,39 +850,45 @@
         <v>37000</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I11" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="E12" s="2">
         <v>37620</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
